--- a/Backend/sample_datasets/Product-Sales-Region.xlsx
+++ b/Backend/sample_datasets/Product-Sales-Region.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/07555edf8d3e3c98/Desktop/AI_Demand_Forecasting/Backend/sample_datasets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_C8261FC465D92C3960256FE51D9CCA1751231278" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4516C7A3-6C8A-4054-AD9C-863CEEC06A90}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_C8261FC465D92C3960256FE51D9CCA1751231278" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F107E2C-6D6A-4A63-8503-3FA77AE1EFF9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="20">
   <si>
     <t>East</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>sales</t>
+  </si>
+  <si>
+    <t>quantity</t>
   </si>
 </sst>
 </file>
@@ -448,14 +451,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>12</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="E1" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>44980</v>
       </c>
@@ -488,8 +494,11 @@
       <c r="E2">
         <v>163.6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45645</v>
       </c>
@@ -505,8 +514,11 @@
       <c r="E3">
         <v>544.01</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45056</v>
       </c>
@@ -522,8 +534,11 @@
       <c r="E4">
         <v>346.18</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>45714</v>
       </c>
@@ -539,8 +554,11 @@
       <c r="E5">
         <v>384.82</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>45101</v>
       </c>
@@ -556,8 +574,11 @@
       <c r="E6">
         <v>237.76</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>45342</v>
       </c>
@@ -573,8 +594,11 @@
       <c r="E7">
         <v>385.09</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>44937</v>
       </c>
@@ -590,8 +614,11 @@
       <c r="E8">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>44935</v>
       </c>
@@ -607,8 +634,11 @@
       <c r="E9">
         <v>330.22</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>45581</v>
       </c>
@@ -624,8 +654,11 @@
       <c r="E10">
         <v>432.04</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>45721</v>
       </c>
@@ -641,8 +674,11 @@
       <c r="E11">
         <v>323.27999999999997</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45392</v>
       </c>
@@ -658,8 +694,11 @@
       <c r="E12">
         <v>523.29</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>45485</v>
       </c>
@@ -675,8 +714,11 @@
       <c r="E13">
         <v>207.35</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>45128</v>
       </c>
@@ -692,8 +734,11 @@
       <c r="E14">
         <v>120.53</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>45675</v>
       </c>
@@ -709,8 +754,11 @@
       <c r="E15">
         <v>157.83000000000001</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>45634</v>
       </c>
@@ -726,8 +774,11 @@
       <c r="E16">
         <v>220.3</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>45788</v>
       </c>
@@ -743,8 +794,11 @@
       <c r="E17">
         <v>162.96</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>44983</v>
       </c>
@@ -760,8 +814,11 @@
       <c r="E18">
         <v>236.11</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>45440</v>
       </c>
@@ -777,8 +834,11 @@
       <c r="E19">
         <v>573.14</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>45260</v>
       </c>
@@ -794,8 +854,11 @@
       <c r="E20">
         <v>519.04</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>45099</v>
       </c>
@@ -811,8 +874,11 @@
       <c r="E21">
         <v>30.83</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>45813</v>
       </c>
@@ -828,8 +894,11 @@
       <c r="E22">
         <v>319.05</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>44988</v>
       </c>
@@ -845,8 +914,11 @@
       <c r="E23">
         <v>312.79000000000002</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>45340</v>
       </c>
@@ -862,8 +934,11 @@
       <c r="E24">
         <v>395.45</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>45144</v>
       </c>
@@ -879,8 +954,11 @@
       <c r="E25">
         <v>472.72</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>45435</v>
       </c>
@@ -896,8 +974,11 @@
       <c r="E26">
         <v>288.01</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>45222</v>
       </c>
@@ -913,8 +994,11 @@
       <c r="E27">
         <v>562.29</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>45824</v>
       </c>
@@ -930,8 +1014,11 @@
       <c r="E28">
         <v>101.73</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>44988</v>
       </c>
@@ -947,8 +1034,11 @@
       <c r="E29">
         <v>279.49</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>45614</v>
       </c>
@@ -964,8 +1054,11 @@
       <c r="E30">
         <v>178.55</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>45055</v>
       </c>
@@ -981,8 +1074,11 @@
       <c r="E31">
         <v>472.07</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>45633</v>
       </c>
@@ -998,8 +1094,11 @@
       <c r="E32">
         <v>306.29000000000002</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>45335</v>
       </c>
@@ -1015,8 +1114,11 @@
       <c r="E33">
         <v>434.77</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>45725</v>
       </c>
@@ -1032,8 +1134,11 @@
       <c r="E34">
         <v>64.98</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>45021</v>
       </c>
@@ -1049,8 +1154,11 @@
       <c r="E35">
         <v>476.49</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>45785</v>
       </c>
@@ -1066,8 +1174,11 @@
       <c r="E36">
         <v>559.72</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>45172</v>
       </c>
@@ -1083,8 +1194,11 @@
       <c r="E37">
         <v>82.14</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>45737</v>
       </c>
@@ -1100,8 +1214,11 @@
       <c r="E38">
         <v>343.21</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>45828</v>
       </c>
@@ -1117,8 +1234,11 @@
       <c r="E39">
         <v>301.01</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>45337</v>
       </c>
@@ -1134,8 +1254,11 @@
       <c r="E40">
         <v>428.13</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>45086</v>
       </c>
@@ -1151,8 +1274,11 @@
       <c r="E41">
         <v>503.28</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>45148</v>
       </c>
@@ -1168,8 +1294,11 @@
       <c r="E42">
         <v>470.32</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>45459</v>
       </c>
@@ -1185,8 +1314,11 @@
       <c r="E43">
         <v>65.17</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>45130</v>
       </c>
@@ -1202,8 +1334,11 @@
       <c r="E44">
         <v>36.17</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>45066</v>
       </c>
@@ -1219,8 +1354,11 @@
       <c r="E45">
         <v>459.31</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45107</v>
       </c>
@@ -1236,8 +1374,11 @@
       <c r="E46">
         <v>416.06</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45447</v>
       </c>
@@ -1253,8 +1394,11 @@
       <c r="E47">
         <v>302.58</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>45691</v>
       </c>
@@ -1270,8 +1414,11 @@
       <c r="E48">
         <v>33.130000000000003</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>45300</v>
       </c>
@@ -1287,8 +1434,11 @@
       <c r="E49">
         <v>582.52</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>45365</v>
       </c>
@@ -1304,8 +1454,11 @@
       <c r="E50">
         <v>165.15</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>45541</v>
       </c>
@@ -1321,8 +1474,11 @@
       <c r="E51">
         <v>242.82</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>45002</v>
       </c>
@@ -1338,8 +1494,11 @@
       <c r="E52">
         <v>65.989999999999995</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>45674</v>
       </c>
@@ -1355,8 +1514,11 @@
       <c r="E53">
         <v>251.69</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>45547</v>
       </c>
@@ -1372,8 +1534,11 @@
       <c r="E54">
         <v>269.41000000000003</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>45296</v>
       </c>
@@ -1389,8 +1554,11 @@
       <c r="E55">
         <v>371.3</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>45401</v>
       </c>
@@ -1406,8 +1574,11 @@
       <c r="E56">
         <v>288.24</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>45819</v>
       </c>
@@ -1423,8 +1594,11 @@
       <c r="E57">
         <v>232.75</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>45722</v>
       </c>
@@ -1440,8 +1614,11 @@
       <c r="E58">
         <v>146.28</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>45070</v>
       </c>
@@ -1457,8 +1634,11 @@
       <c r="E59">
         <v>100.38</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>44953</v>
       </c>
@@ -1474,8 +1654,11 @@
       <c r="E60">
         <v>375.48</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>45372</v>
       </c>
@@ -1491,8 +1674,11 @@
       <c r="E61">
         <v>316.89</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>45682</v>
       </c>
@@ -1508,8 +1694,11 @@
       <c r="E62">
         <v>295.06</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>45089</v>
       </c>
@@ -1525,8 +1714,11 @@
       <c r="E63">
         <v>301.68</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>45738</v>
       </c>
@@ -1542,8 +1734,11 @@
       <c r="E64">
         <v>475.39</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F64">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>45346</v>
       </c>
@@ -1559,8 +1754,11 @@
       <c r="E65">
         <v>47.25</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F65">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>45269</v>
       </c>
@@ -1576,8 +1774,11 @@
       <c r="E66">
         <v>511.17</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F66">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>45200</v>
       </c>
@@ -1593,8 +1794,11 @@
       <c r="E67">
         <v>66.58</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F67">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>45138</v>
       </c>
@@ -1610,8 +1814,11 @@
       <c r="E68">
         <v>490.52</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F68">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>45650</v>
       </c>
@@ -1627,8 +1834,11 @@
       <c r="E69">
         <v>405.96</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F69">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>45611</v>
       </c>
@@ -1644,8 +1854,11 @@
       <c r="E70">
         <v>159.41</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>45729</v>
       </c>
@@ -1661,8 +1874,11 @@
       <c r="E71">
         <v>38.49</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>45354</v>
       </c>
@@ -1678,8 +1894,11 @@
       <c r="E72">
         <v>328.36</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>44968</v>
       </c>
@@ -1695,8 +1914,11 @@
       <c r="E73">
         <v>548.01</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F73">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>45225</v>
       </c>
@@ -1712,8 +1934,11 @@
       <c r="E74">
         <v>484.45</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>45220</v>
       </c>
@@ -1729,8 +1954,11 @@
       <c r="E75">
         <v>195.84</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F75">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>45305</v>
       </c>
@@ -1746,8 +1974,11 @@
       <c r="E76">
         <v>29.94</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F76">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>45134</v>
       </c>
@@ -1763,8 +1994,11 @@
       <c r="E77">
         <v>553.91</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>45588</v>
       </c>
@@ -1780,8 +2014,11 @@
       <c r="E78">
         <v>445.52</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>45195</v>
       </c>
@@ -1797,8 +2034,11 @@
       <c r="E79">
         <v>551.58000000000004</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>45276</v>
       </c>
@@ -1814,8 +2054,11 @@
       <c r="E80">
         <v>241.4</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>45293</v>
       </c>
@@ -1831,8 +2074,11 @@
       <c r="E81">
         <v>351.93</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>45338</v>
       </c>
@@ -1848,8 +2094,11 @@
       <c r="E82">
         <v>83.75</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>45415</v>
       </c>
@@ -1865,8 +2114,11 @@
       <c r="E83">
         <v>416.95</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>45073</v>
       </c>
@@ -1882,8 +2134,11 @@
       <c r="E84">
         <v>142.43</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>44931</v>
       </c>
@@ -1899,8 +2154,11 @@
       <c r="E85">
         <v>582.52</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>45798</v>
       </c>
@@ -1916,8 +2174,11 @@
       <c r="E86">
         <v>129.56</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>45128</v>
       </c>
@@ -1933,8 +2194,11 @@
       <c r="E87">
         <v>431.82</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>45802</v>
       </c>
@@ -1950,8 +2214,11 @@
       <c r="E88">
         <v>15.85</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>45612</v>
       </c>
@@ -1967,8 +2234,11 @@
       <c r="E89">
         <v>548.34</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>45249</v>
       </c>
@@ -1984,8 +2254,11 @@
       <c r="E90">
         <v>525.83000000000004</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F90">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>45669</v>
       </c>
@@ -2001,8 +2274,11 @@
       <c r="E91">
         <v>411.38</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>45014</v>
       </c>
@@ -2018,8 +2294,11 @@
       <c r="E92">
         <v>559.95000000000005</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F92">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>45717</v>
       </c>
@@ -2035,8 +2314,11 @@
       <c r="E93">
         <v>179.9</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F93">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>45217</v>
       </c>
@@ -2052,8 +2334,11 @@
       <c r="E94">
         <v>494.15</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F94">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>45760</v>
       </c>
@@ -2069,8 +2354,11 @@
       <c r="E95">
         <v>462.99</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F95">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>45790</v>
       </c>
@@ -2086,8 +2374,11 @@
       <c r="E96">
         <v>460.24</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F96">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>45403</v>
       </c>
@@ -2103,8 +2394,11 @@
       <c r="E97">
         <v>309.52</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F97">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>45688</v>
       </c>
@@ -2120,8 +2414,11 @@
       <c r="E98">
         <v>323.83</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F98">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>45730</v>
       </c>
@@ -2137,8 +2434,11 @@
       <c r="E99">
         <v>503.07</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>45438</v>
       </c>
@@ -2154,8 +2454,11 @@
       <c r="E100">
         <v>491.68</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F100">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>45129</v>
       </c>
@@ -2171,8 +2474,11 @@
       <c r="E101">
         <v>468.45</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F101">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>45372</v>
       </c>
@@ -2188,8 +2494,11 @@
       <c r="E102">
         <v>401.76</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F102">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>45021</v>
       </c>
@@ -2205,8 +2514,11 @@
       <c r="E103">
         <v>221</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F103">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>45530</v>
       </c>
@@ -2222,8 +2534,11 @@
       <c r="E104">
         <v>188.45</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F104">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>45480</v>
       </c>
@@ -2239,8 +2554,11 @@
       <c r="E105">
         <v>566.20000000000005</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F105">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>45198</v>
       </c>
@@ -2256,8 +2574,11 @@
       <c r="E106">
         <v>167.09</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F106">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>45203</v>
       </c>
@@ -2273,8 +2594,11 @@
       <c r="E107">
         <v>36.159999999999997</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F107">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>45817</v>
       </c>
@@ -2290,8 +2614,11 @@
       <c r="E108">
         <v>73.94</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F108">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>45820</v>
       </c>
@@ -2307,8 +2634,11 @@
       <c r="E109">
         <v>459.49</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F109">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>45472</v>
       </c>
@@ -2324,8 +2654,11 @@
       <c r="E110">
         <v>168.05</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F110">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>45374</v>
       </c>
@@ -2341,8 +2674,11 @@
       <c r="E111">
         <v>37.54</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F111">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>45487</v>
       </c>
@@ -2358,8 +2694,11 @@
       <c r="E112">
         <v>151.16</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F112">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>45366</v>
       </c>
@@ -2375,8 +2714,11 @@
       <c r="E113">
         <v>78.58</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F113">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>45766</v>
       </c>
@@ -2392,8 +2734,11 @@
       <c r="E114">
         <v>37.33</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F114">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>45337</v>
       </c>
@@ -2409,8 +2754,11 @@
       <c r="E115">
         <v>537.02</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F115">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>45316</v>
       </c>
@@ -2426,8 +2774,11 @@
       <c r="E116">
         <v>215.6</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F116">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>45762</v>
       </c>
@@ -2443,8 +2794,11 @@
       <c r="E117">
         <v>209.5</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F117">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>45762</v>
       </c>
@@ -2460,8 +2814,11 @@
       <c r="E118">
         <v>348.98</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F118">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>45515</v>
       </c>
@@ -2477,8 +2834,11 @@
       <c r="E119">
         <v>289.14</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F119">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>45261</v>
       </c>
@@ -2494,8 +2854,11 @@
       <c r="E120">
         <v>396.93</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F120">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>45144</v>
       </c>
@@ -2511,8 +2874,11 @@
       <c r="E121">
         <v>508.57</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F121">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>45315</v>
       </c>
@@ -2528,8 +2894,11 @@
       <c r="E122">
         <v>259.61</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F122">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>45358</v>
       </c>
@@ -2545,8 +2914,11 @@
       <c r="E123">
         <v>313.29000000000002</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>45313</v>
       </c>
@@ -2562,8 +2934,11 @@
       <c r="E124">
         <v>106.57</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F124">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>44980</v>
       </c>
@@ -2579,8 +2954,11 @@
       <c r="E125">
         <v>109</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F125">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>45091</v>
       </c>
@@ -2596,8 +2974,11 @@
       <c r="E126">
         <v>323.8</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F126">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>45790</v>
       </c>
@@ -2613,8 +2994,11 @@
       <c r="E127">
         <v>384.32</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F127">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>45503</v>
       </c>
@@ -2630,8 +3014,11 @@
       <c r="E128">
         <v>163.86</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F128">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>45491</v>
       </c>
@@ -2647,8 +3034,11 @@
       <c r="E129">
         <v>23.41</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F129">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>45530</v>
       </c>
@@ -2664,8 +3054,11 @@
       <c r="E130">
         <v>488.9</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F130">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>45816</v>
       </c>
@@ -2681,8 +3074,11 @@
       <c r="E131">
         <v>452.56</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F131">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>45793</v>
       </c>
@@ -2698,8 +3094,11 @@
       <c r="E132">
         <v>465.24</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F132">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>45491</v>
       </c>
@@ -2715,8 +3114,11 @@
       <c r="E133">
         <v>442.65</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F133">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>45186</v>
       </c>
@@ -2732,8 +3134,11 @@
       <c r="E134">
         <v>469.44</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F134">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>44998</v>
       </c>
@@ -2749,8 +3154,11 @@
       <c r="E135">
         <v>248.77</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F135">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>45014</v>
       </c>
@@ -2766,8 +3174,11 @@
       <c r="E136">
         <v>565.29</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F136">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>45121</v>
       </c>
@@ -2783,8 +3194,11 @@
       <c r="E137">
         <v>244.8</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F137">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>45373</v>
       </c>
@@ -2800,8 +3214,11 @@
       <c r="E138">
         <v>290.93</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F138">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>45426</v>
       </c>
@@ -2817,8 +3234,11 @@
       <c r="E139">
         <v>229.49</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F139">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>45076</v>
       </c>
@@ -2834,8 +3254,11 @@
       <c r="E140">
         <v>427.36</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F140">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>45004</v>
       </c>
@@ -2851,8 +3274,11 @@
       <c r="E141">
         <v>443.51</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F141">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>45147</v>
       </c>
@@ -2868,8 +3294,11 @@
       <c r="E142">
         <v>280.63</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F142">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>45578</v>
       </c>
@@ -2885,8 +3314,11 @@
       <c r="E143">
         <v>416.66</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F143">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>45705</v>
       </c>
@@ -2902,8 +3334,11 @@
       <c r="E144">
         <v>589.48</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F144">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>45819</v>
       </c>
@@ -2919,8 +3354,11 @@
       <c r="E145">
         <v>152.84</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F145">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>45411</v>
       </c>
@@ -2936,8 +3374,11 @@
       <c r="E146">
         <v>163.66</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F146">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>45003</v>
       </c>
@@ -2953,8 +3394,11 @@
       <c r="E147">
         <v>484.25</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F147">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>45647</v>
       </c>
@@ -2970,8 +3414,11 @@
       <c r="E148">
         <v>380.4</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F148">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>45039</v>
       </c>
@@ -2987,8 +3434,11 @@
       <c r="E149">
         <v>332.38</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F149">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>45788</v>
       </c>
@@ -3004,8 +3454,11 @@
       <c r="E150">
         <v>210.94</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F150">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>45354</v>
       </c>
@@ -3021,8 +3474,11 @@
       <c r="E151">
         <v>382.8</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F151">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>45677</v>
       </c>
@@ -3038,8 +3494,11 @@
       <c r="E152">
         <v>386.29</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F152">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>45738</v>
       </c>
@@ -3055,8 +3514,11 @@
       <c r="E153">
         <v>225.99</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F153">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>45744</v>
       </c>
@@ -3072,8 +3534,11 @@
       <c r="E154">
         <v>312.56</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F154">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>45705</v>
       </c>
@@ -3089,8 +3554,11 @@
       <c r="E155">
         <v>433.77</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F155">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>45604</v>
       </c>
@@ -3106,8 +3574,11 @@
       <c r="E156">
         <v>159.33000000000001</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F156">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>45368</v>
       </c>
@@ -3123,8 +3594,11 @@
       <c r="E157">
         <v>32.229999999999997</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F157">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>45167</v>
       </c>
@@ -3140,8 +3614,11 @@
       <c r="E158">
         <v>527.77</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F158">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>45099</v>
       </c>
@@ -3157,8 +3634,11 @@
       <c r="E159">
         <v>291.08999999999997</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F159">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>45346</v>
       </c>
@@ -3174,8 +3654,11 @@
       <c r="E160">
         <v>350.12</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F160">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>45392</v>
       </c>
@@ -3191,8 +3674,11 @@
       <c r="E161">
         <v>195.26</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F161">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>45060</v>
       </c>
@@ -3208,8 +3694,11 @@
       <c r="E162">
         <v>291.10000000000002</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F162">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>44996</v>
       </c>
@@ -3225,8 +3714,11 @@
       <c r="E163">
         <v>93.92</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F163">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>45528</v>
       </c>
@@ -3242,8 +3734,11 @@
       <c r="E164">
         <v>15.92</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F164">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>45345</v>
       </c>
@@ -3259,8 +3754,11 @@
       <c r="E165">
         <v>120.22</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F165">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>45321</v>
       </c>
@@ -3276,8 +3774,11 @@
       <c r="E166">
         <v>118.8</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F166">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>45314</v>
       </c>
@@ -3293,8 +3794,11 @@
       <c r="E167">
         <v>92.45</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F167">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>44931</v>
       </c>
@@ -3310,8 +3814,11 @@
       <c r="E168">
         <v>463.51</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F168">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>45281</v>
       </c>
@@ -3327,8 +3834,11 @@
       <c r="E169">
         <v>284.7</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F169">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>45071</v>
       </c>
@@ -3344,8 +3854,11 @@
       <c r="E170">
         <v>343.25</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F170">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>45838</v>
       </c>
@@ -3361,8 +3874,11 @@
       <c r="E171">
         <v>95.24</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F171">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>45700</v>
       </c>
@@ -3378,8 +3894,11 @@
       <c r="E172">
         <v>104.8</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F172">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>45294</v>
       </c>
@@ -3395,8 +3914,11 @@
       <c r="E173">
         <v>164.31</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F173">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>44960</v>
       </c>
@@ -3412,8 +3934,11 @@
       <c r="E174">
         <v>325.18</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F174">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>45352</v>
       </c>
@@ -3429,8 +3954,11 @@
       <c r="E175">
         <v>542.82000000000005</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F175">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>45070</v>
       </c>
@@ -3446,8 +3974,11 @@
       <c r="E176">
         <v>207.48</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F176">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>45830</v>
       </c>
@@ -3463,8 +3994,11 @@
       <c r="E177">
         <v>527.88</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F177">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>45026</v>
       </c>
@@ -3480,8 +4014,11 @@
       <c r="E178">
         <v>71.209999999999994</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F178">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>45720</v>
       </c>
@@ -3497,8 +4034,11 @@
       <c r="E179">
         <v>486.07</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F179">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>45484</v>
       </c>
@@ -3514,8 +4054,11 @@
       <c r="E180">
         <v>555.03</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F180">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>45521</v>
       </c>
@@ -3531,8 +4074,11 @@
       <c r="E181">
         <v>421.08</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F181">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>45838</v>
       </c>
@@ -3548,8 +4094,11 @@
       <c r="E182">
         <v>76.17</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F182">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>45602</v>
       </c>
@@ -3565,8 +4114,11 @@
       <c r="E183">
         <v>503.55</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F183">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>45748</v>
       </c>
@@ -3582,8 +4134,11 @@
       <c r="E184">
         <v>31.56</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F184">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>45474</v>
       </c>
@@ -3599,8 +4154,11 @@
       <c r="E185">
         <v>72.92</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F185">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>45269</v>
       </c>
@@ -3616,8 +4174,11 @@
       <c r="E186">
         <v>421.93</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F186">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>45104</v>
       </c>
@@ -3633,8 +4194,11 @@
       <c r="E187">
         <v>478.41</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F187">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>45121</v>
       </c>
@@ -3650,8 +4214,11 @@
       <c r="E188">
         <v>501.74</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F188">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>44965</v>
       </c>
@@ -3667,8 +4234,11 @@
       <c r="E189">
         <v>247.53</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F189">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>45471</v>
       </c>
@@ -3684,8 +4254,11 @@
       <c r="E190">
         <v>176.51</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F190">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>45397</v>
       </c>
@@ -3701,8 +4274,11 @@
       <c r="E191">
         <v>143.43</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F191">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>45257</v>
       </c>
@@ -3718,8 +4294,11 @@
       <c r="E192">
         <v>538.5</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F192">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>45743</v>
       </c>
@@ -3735,8 +4314,11 @@
       <c r="E193">
         <v>87.17</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F193">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>45144</v>
       </c>
@@ -3752,8 +4334,11 @@
       <c r="E194">
         <v>498.32</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F194">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>45639</v>
       </c>
@@ -3769,8 +4354,11 @@
       <c r="E195">
         <v>57.14</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F195">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>45674</v>
       </c>
@@ -3786,8 +4374,11 @@
       <c r="E196">
         <v>124.18</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F196">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>45256</v>
       </c>
@@ -3803,8 +4394,11 @@
       <c r="E197">
         <v>107.45</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F197">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>44971</v>
       </c>
@@ -3820,8 +4414,11 @@
       <c r="E198">
         <v>411.26</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F198">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>45690</v>
       </c>
@@ -3837,8 +4434,11 @@
       <c r="E199">
         <v>248.1</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F199">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>45027</v>
       </c>
@@ -3853,6 +4453,9 @@
       </c>
       <c r="E200">
         <v>486.52</v>
+      </c>
+      <c r="F200">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
